--- a/artfynd/A 69544-2021 artfynd.xlsx
+++ b/artfynd/A 69544-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119594480</v>
+        <v>119594488</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>77548</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Geoglossum umbratile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Sacc.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, Ång</t>
+          <t>Svanaträsket, O om, infarten till stranden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679183</v>
+        <v>679266</v>
       </c>
       <c r="R2" t="n">
-        <v>7101009</v>
+        <v>7101073</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,8 +762,23 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>2024004</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119594488</v>
+        <v>119594483</v>
       </c>
       <c r="B3" t="n">
-        <v>77548</v>
+        <v>91856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +807,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4202</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, infarten till stranden, Ång</t>
+          <t>Svanaträsket, O om, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679266</v>
+        <v>679168</v>
       </c>
       <c r="R3" t="n">
-        <v>7101073</v>
+        <v>7101167</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,23 +879,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>2024004</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119594482</v>
+        <v>119594486</v>
       </c>
       <c r="B4" t="n">
-        <v>77558</v>
+        <v>91840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,37 +913,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6254</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hårjordtunga</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Trichoglossum hirsutum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boud.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svanaträskets O sida, vid stranden, Ång</t>
+          <t>Svanaträsket, O om, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679203</v>
+        <v>679176</v>
       </c>
       <c r="R4" t="n">
-        <v>7101059</v>
+        <v>7101167</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,23 +981,8 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>2024005</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1017,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119594483</v>
+        <v>119594480</v>
       </c>
       <c r="B5" t="n">
-        <v>91856</v>
+        <v>91852</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679168</v>
+        <v>679183</v>
       </c>
       <c r="R5" t="n">
-        <v>7101167</v>
+        <v>7101009</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1119,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119594486</v>
+        <v>119594482</v>
       </c>
       <c r="B6" t="n">
-        <v>91840</v>
+        <v>77558</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,34 +1117,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6254</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hårjordtunga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Trichoglossum hirsutum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Boud.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, Ång</t>
+          <t>Svanaträskets O sida, vid stranden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679176</v>
+        <v>679203</v>
       </c>
       <c r="R6" t="n">
-        <v>7101167</v>
+        <v>7101059</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,8 +1188,23 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>2024005</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 69544-2021 artfynd.xlsx
+++ b/artfynd/A 69544-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119594488</v>
+        <v>119594480</v>
       </c>
       <c r="B2" t="n">
-        <v>77548</v>
+        <v>91852</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4202</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sacc.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, infarten till stranden, Ång</t>
+          <t>Svanaträsket, O om, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679266</v>
+        <v>679183</v>
       </c>
       <c r="R2" t="n">
-        <v>7101073</v>
+        <v>7101009</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -762,23 +759,8 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>2024004</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -795,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119594483</v>
+        <v>119594488</v>
       </c>
       <c r="B3" t="n">
-        <v>91856</v>
+        <v>77548</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,38 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Geoglossum umbratile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Sacc.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, Ång</t>
+          <t>Svanaträsket, O om, infarten till stranden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679168</v>
+        <v>679266</v>
       </c>
       <c r="R3" t="n">
-        <v>7101167</v>
+        <v>7101073</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,8 +864,23 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2024004</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119594486</v>
+        <v>119594482</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>77558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,34 +913,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6254</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hårjordtunga</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Trichoglossum hirsutum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Boud.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, Ång</t>
+          <t>Svanaträskets O sida, vid stranden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>679176</v>
+        <v>679203</v>
       </c>
       <c r="R4" t="n">
-        <v>7101167</v>
+        <v>7101059</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,8 +984,23 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>2024005</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -999,10 +1017,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119594480</v>
+        <v>119594486</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,21 +1033,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679183</v>
+        <v>679176</v>
       </c>
       <c r="R5" t="n">
-        <v>7101009</v>
+        <v>7101167</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1101,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119594482</v>
+        <v>119594483</v>
       </c>
       <c r="B6" t="n">
-        <v>77558</v>
+        <v>91856</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,41 +1131,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6254</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hårjordtunga</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichoglossum hirsutum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Boud.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanaträskets O sida, vid stranden, Ång</t>
+          <t>Svanaträsket, O om, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679203</v>
+        <v>679168</v>
       </c>
       <c r="R6" t="n">
-        <v>7101059</v>
+        <v>7101167</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1188,23 +1203,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>2024005</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 69544-2021 artfynd.xlsx
+++ b/artfynd/A 69544-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119594480</v>
+        <v>119594486</v>
       </c>
       <c r="B2" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>679183</v>
+        <v>679176</v>
       </c>
       <c r="R2" t="n">
-        <v>7101009</v>
+        <v>7101167</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119594488</v>
+        <v>119594480</v>
       </c>
       <c r="B3" t="n">
-        <v>77548</v>
+        <v>91852</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4202</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart jordtunga</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Geoglossum umbratile</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sacc.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, infarten till stranden, Ång</t>
+          <t>Svanaträsket, O om, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>679266</v>
+        <v>679183</v>
       </c>
       <c r="R3" t="n">
-        <v>7101073</v>
+        <v>7101009</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -864,23 +861,8 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Gudrun Norstedt</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>2024004</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1017,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119594486</v>
+        <v>119594483</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,25 +1011,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1057,7 +1039,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>679176</v>
+        <v>679168</v>
       </c>
       <c r="R5" t="n">
         <v>7101167</v>
@@ -1119,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119594483</v>
+        <v>119594488</v>
       </c>
       <c r="B6" t="n">
-        <v>91856</v>
+        <v>77548</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,38 +1113,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart jordtunga</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Geoglossum umbratile</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Sacc.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Svanaträsket, O om, Ång</t>
+          <t>Svanaträsket, O om, infarten till stranden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>679168</v>
+        <v>679266</v>
       </c>
       <c r="R6" t="n">
-        <v>7101167</v>
+        <v>7101073</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1203,8 +1188,23 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>Gudrun Norstedt</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>2024004</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">

--- a/artfynd/A 69544-2021 artfynd.xlsx
+++ b/artfynd/A 69544-2021 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>119594488</v>
       </c>
       <c r="B6" t="n">
-        <v>77638</v>
+        <v>77651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
